--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18EC9B28-B57F-40CC-845F-5634C7D64715}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8EFC223-5593-4501-A134-C0E4095D8347}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="6" activeTab="10" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="11" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="22_07 a 03_08" sheetId="9" r:id="rId9"/>
     <sheet name="04_ a 11_08" sheetId="10" r:id="rId10"/>
     <sheet name="12_ a 18_08" sheetId="11" r:id="rId11"/>
+    <sheet name="19 a 25_8" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="171">
   <si>
     <t>Código</t>
   </si>
@@ -546,6 +547,27 @@
   </si>
   <si>
     <t xml:space="preserve">Total de ocorrências:  </t>
+  </si>
+  <si>
+    <t>CCAV</t>
+  </si>
+  <si>
+    <t>CGRV</t>
+  </si>
+  <si>
+    <t>CAAS</t>
+  </si>
+  <si>
+    <t>CNAS</t>
+  </si>
+  <si>
+    <t>GTRC</t>
+  </si>
+  <si>
+    <t>GTNO-SIA</t>
+  </si>
+  <si>
+    <t>GTSI</t>
   </si>
 </sst>
 </file>
@@ -670,6 +692,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2466,6 +2492,579 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C941FAF-CE5A-4A72-91C6-F6E59E534655}">
+  <dimension ref="A2:C53"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C53</f>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>38</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>28</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="8">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="8">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>31</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>37</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>3</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>6</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>27</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>2</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>7</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>43</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>5</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>4</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>26</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>30</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>15</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>45</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>40</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>46</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>21</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>19</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>9</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>0</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>10</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>11</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>14</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>12</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>25</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>23</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>18</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>24</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>20</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>32</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>39</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>36</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>33</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>35</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>42</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>41</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>44</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>47</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C53" s="10">
+        <f>SUM(C5:C52)</f>
+        <v>248</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -2780,7 +3379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>57</v>
       </c>
@@ -2900,7 +3499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>39</v>
       </c>

--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://anac-my.sharepoint.com/personal/luiz_beltrao_anac_gov_br/Documents/7 - CGDIN/SEI/Verificação semanal LGPD/Painel de controle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8EFC223-5593-4501-A134-C0E4095D8347}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{B08CBB39-7D29-48D2-BF0D-F3F98B4AE0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9B72770-B707-4C39-A25C-B65B3F3ECE7A}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="7" activeTab="11" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="8" activeTab="12" xr2:uid="{A9AF6F09-8019-4632-99BD-44582E7A76AD}"/>
   </bookViews>
   <sheets>
     <sheet name="1 a 8.06" sheetId="2" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="04_ a 11_08" sheetId="10" r:id="rId10"/>
     <sheet name="12_ a 18_08" sheetId="11" r:id="rId11"/>
     <sheet name="19 a 25_8" sheetId="12" r:id="rId12"/>
+    <sheet name="26 a 01_09" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'07 a 13.07'!$A$4:$B$4</definedName>
@@ -55,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="174">
   <si>
     <t>Código</t>
   </si>
@@ -568,6 +569,15 @@
   </si>
   <si>
     <t>GTSI</t>
+  </si>
+  <si>
+    <t>GEAM</t>
+  </si>
+  <si>
+    <t>GFIC</t>
+  </si>
+  <si>
+    <t>SAG</t>
   </si>
 </sst>
 </file>
@@ -639,7 +649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -676,6 +686,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3065,6 +3078,602 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A49491A-8C96-4B55-A1BC-3ECC09E8ADFD}">
+  <dimension ref="A2:C56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.36328125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" s="11">
+        <f>C56</f>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="8">
+        <v>41</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="8">
+        <v>32</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="8">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>31</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" s="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>3</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>34</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="8">
+        <v>37</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>17</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>5</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="8">
+        <v>40</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>46</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="8">
+        <v>29</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="8">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8">
+        <v>48</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>7</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>42</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="8">
+        <v>14</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" s="8">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8">
+        <v>12</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8">
+        <v>33</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" s="8">
+        <v>39</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" s="8">
+        <v>30</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="8">
+        <v>18</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="8">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C27" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="8">
+        <v>21</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>24</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" s="8">
+        <v>25</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="8">
+        <v>4</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" s="8">
+        <v>9</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="8">
+        <v>11</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="8">
+        <v>8</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="8">
+        <v>6</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="8">
+        <v>2</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8">
+        <v>0</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="8">
+        <v>1</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="8">
+        <v>15</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="8">
+        <v>10</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" s="8">
+        <v>27</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" s="8">
+        <v>28</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" s="8">
+        <v>20</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C43" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" s="8">
+        <v>19</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="8">
+        <v>23</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" s="8">
+        <v>22</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" s="8">
+        <v>38</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" s="8">
+        <v>36</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8">
+        <v>35</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="8">
+        <v>43</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C50" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="8">
+        <v>45</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="8">
+        <v>44</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="8">
+        <v>47</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8">
+        <v>49</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C56" s="13">
+        <f>SUM(C5:C55)</f>
+        <v>238</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DC5A72-105B-4A74-9A40-6DECF5B03B2D}">
   <dimension ref="A2:B61"/>
@@ -6827,6 +7436,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -7055,27 +7684,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="583a6060-d1b7-45db-b4d6-660de356d713">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="97cc50e0-5e48-4896-9dff-357abd4c15c7" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7092,29 +7726,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="583a6060-d1b7-45db-b4d6-660de356d713"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="97cc50e0-5e48-4896-9dff-357abd4c15c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/ocorrencias.xlsx
+++ b/ocorrencias.xlsx
@@ -7447,15 +7447,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B2C160DC8B30F54783CACC61231B8252" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="1f908957678d77794d61d7fffe93fc41">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="583a6060-d1b7-45db-b4d6-660de356d713" xmlns:ns3="97cc50e0-5e48-4896-9dff-357abd4c15c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0aa59e2dacabcbe879c9d2919b50461b" ns2:_="" ns3:_="">
     <xsd:import namespace="583a6060-d1b7-45db-b4d6-660de356d713"/>
@@ -7684,6 +7675,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD91E5EA-D116-4795-B575-F86A672AE76F}">
   <ds:schemaRefs>
@@ -7702,14 +7702,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{907A6689-E3B8-4B0E-A078-95B4FF1401C0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7726,4 +7718,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BDE4EE3-4557-4002-B14D-2B12156DBD9E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>